--- a/output/graficos_envejecimiento/plot_comunal_d_enveje_a_2024_maule.xlsx
+++ b/output/graficos_envejecimiento/plot_comunal_d_enveje_a_2024_maule.xlsx
@@ -413,7 +413,7 @@
         <v>17.2922431065738</v>
       </c>
       <c r="D3">
-        <v>62.39290144070223</v>
+        <v>62.39290144070222</v>
       </c>
       <c r="E3">
         <v>20.31485545272398</v>
@@ -435,7 +435,7 @@
         <v>54.61738968534723</v>
       </c>
       <c r="E4">
-        <v>32.61031465276485</v>
+        <v>32.61031465276484</v>
       </c>
     </row>
     <row r="5">
@@ -489,10 +489,10 @@
         <v>15.57434266656325</v>
       </c>
       <c r="D7">
-        <v>60.12564957729001</v>
+        <v>60.12564957728999</v>
       </c>
       <c r="E7">
-        <v>24.30000775614675</v>
+        <v>24.30000775614674</v>
       </c>
     </row>
     <row r="8">
@@ -524,13 +524,13 @@
         <v>146.936502042332</v>
       </c>
       <c r="C9">
-        <v>16.55397098598475</v>
+        <v>16.55397098598476</v>
       </c>
       <c r="D9">
-        <v>59.12220309810671</v>
+        <v>59.12220309810672</v>
       </c>
       <c r="E9">
-        <v>24.32382591590853</v>
+        <v>24.32382591590854</v>
       </c>
     </row>
     <row r="10">
@@ -568,7 +568,7 @@
         <v>61.96346026854501</v>
       </c>
       <c r="E11">
-        <v>22.53283439724118</v>
+        <v>22.53283439724117</v>
       </c>
     </row>
     <row r="12">
@@ -641,10 +641,10 @@
         <v>16.84682417524536</v>
       </c>
       <c r="D15">
-        <v>63.10565403905916</v>
+        <v>63.10565403905917</v>
       </c>
       <c r="E15">
-        <v>20.04752178569547</v>
+        <v>20.04752178569548</v>
       </c>
     </row>
     <row r="16">
@@ -676,7 +676,7 @@
         <v>175.0219876868953</v>
       </c>
       <c r="C17">
-        <v>14.80661544471936</v>
+        <v>14.80661544471937</v>
       </c>
       <c r="D17">
         <v>59.27855189477797</v>
@@ -698,7 +698,7 @@
         <v>16.89200884700452</v>
       </c>
       <c r="D18">
-        <v>60.8308491201077</v>
+        <v>60.83084912010771</v>
       </c>
       <c r="E18">
         <v>22.27714203288778</v>
@@ -717,10 +717,10 @@
         <v>16.24481876708704</v>
       </c>
       <c r="D19">
-        <v>59.67016491754123</v>
+        <v>59.67016491754124</v>
       </c>
       <c r="E19">
-        <v>24.08501631537172</v>
+        <v>24.08501631537173</v>
       </c>
     </row>
     <row r="20">
@@ -733,13 +733,13 @@
         <v>130.3517283201941</v>
       </c>
       <c r="C20">
-        <v>16.30493894299698</v>
+        <v>16.30493894299699</v>
       </c>
       <c r="D20">
-        <v>62.44129134325406</v>
+        <v>62.44129134325407</v>
       </c>
       <c r="E20">
-        <v>21.25376971374895</v>
+        <v>21.25376971374896</v>
       </c>
     </row>
     <row r="21">
@@ -755,7 +755,7 @@
         <v>14.90274599542334</v>
       </c>
       <c r="D21">
-        <v>61.45118230358505</v>
+        <v>61.45118230358506</v>
       </c>
       <c r="E21">
         <v>23.64607170099161</v>
@@ -771,13 +771,13 @@
         <v>145.1840549303834</v>
       </c>
       <c r="C22">
-        <v>15.98524345254429</v>
+        <v>15.98524345254428</v>
       </c>
       <c r="D22">
-        <v>60.80673191255831</v>
+        <v>60.8067319125583</v>
       </c>
       <c r="E22">
-        <v>23.20802463489741</v>
+        <v>23.2080246348974</v>
       </c>
     </row>
     <row r="23">
@@ -850,7 +850,7 @@
         <v>16.07096201076449</v>
       </c>
       <c r="D26">
-        <v>60.89773736740346</v>
+        <v>60.89773736740347</v>
       </c>
       <c r="E26">
         <v>23.03130062183205</v>
@@ -869,7 +869,7 @@
         <v>16.44911723864313</v>
       </c>
       <c r="D27">
-        <v>59.66078159095417</v>
+        <v>59.66078159095418</v>
       </c>
       <c r="E27">
         <v>23.8901011704027</v>
@@ -891,7 +891,7 @@
         <v>58.77872619829284</v>
       </c>
       <c r="E28">
-        <v>24.69687021230028</v>
+        <v>24.69687021230029</v>
       </c>
     </row>
     <row r="29">
@@ -907,7 +907,7 @@
         <v>17.90288053479551</v>
       </c>
       <c r="D29">
-        <v>59.79081383558042</v>
+        <v>59.79081383558043</v>
       </c>
       <c r="E29">
         <v>22.30630562962407</v>
@@ -923,13 +923,13 @@
         <v>147.100063734863</v>
       </c>
       <c r="C30">
-        <v>16.7057069846678</v>
+        <v>16.70570698466781</v>
       </c>
       <c r="D30">
         <v>58.72018739352641</v>
       </c>
       <c r="E30">
-        <v>24.57410562180579</v>
+        <v>24.5741056218058</v>
       </c>
     </row>
     <row r="31">
@@ -942,10 +942,10 @@
         <v>134.3579978237214</v>
       </c>
       <c r="C31">
-        <v>16.72353396114826</v>
+        <v>16.72353396114827</v>
       </c>
       <c r="D31">
-        <v>60.80706064328284</v>
+        <v>60.80706064328283</v>
       </c>
       <c r="E31">
         <v>22.4694053955689</v>
